--- a/Developer/Tests/TestMemoryMap.xlsx
+++ b/Developer/Tests/TestMemoryMap.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE0F301E-0C63-4F43-A1D8-D4361F1F8F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EA9B21E-4EDA-420F-AC03-713561D0A257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test1" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="75">
-  <si>
-    <t>Var ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="76">
+  <si>
+    <t>Var Name</t>
   </si>
   <si>
     <t>Data Type</t>
@@ -77,13 +77,16 @@
     <t>-</t>
   </si>
   <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>READ INT8</t>
+  </si>
+  <si>
+    <t>int8_t</t>
+  </si>
+  <si>
     <t>NO</t>
-  </si>
-  <si>
-    <t>READ INT8</t>
-  </si>
-  <si>
-    <t>int8_t</t>
   </si>
   <si>
     <t>READ UINT16</t>
@@ -1871,7 +1874,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5E41BE5-2418-45E1-9408-F1310391CD92}" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" headerRowBorderDxfId="41" tableBorderDxfId="42" totalsRowBorderDxfId="40">
   <autoFilter ref="A1:J15" xr:uid="{C5E41BE5-2418-45E1-9408-F1310391CD92}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{5A8A2FFC-7543-4BD3-8E21-35E3E379BAF9}" name="Var ID" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{5A8A2FFC-7543-4BD3-8E21-35E3E379BAF9}" name="Var Name" dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{F5CB57F1-4036-4329-94B4-4C83171E4D3B}" name="Data Type" dataDxfId="38"/>
     <tableColumn id="3" xr3:uid="{9157E660-741E-49DB-A4B9-01858ABD9B8E}" name="External Access" dataDxfId="37"/>
     <tableColumn id="4" xr3:uid="{C6E2351D-F5F9-4C3A-9F5B-898DD6E6EBBE}" name="Units" dataDxfId="36"/>
@@ -1892,7 +1895,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{08EF77C3-AB38-4C16-99C3-559D0476E452}" name="Table110" displayName="Table110" ref="A1:J15" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:J15" xr:uid="{C5E41BE5-2418-45E1-9408-F1310391CD92}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{01376FE5-E184-40DB-990D-90567B30290C}" name="Var ID" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{01376FE5-E184-40DB-990D-90567B30290C}" name="Var Name" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{06E9C7B2-01AD-412F-BA9B-A712046F2989}" name="Data Type" dataDxfId="23"/>
     <tableColumn id="3" xr3:uid="{AF42F784-40E0-4256-B1AA-FDD64307F3D1}" name="External Access" dataDxfId="22"/>
     <tableColumn id="4" xr3:uid="{2A808460-9437-4D34-9187-9FF07695CDE3}" name="Units" dataDxfId="21"/>
@@ -1911,7 +1914,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{1110C33E-B834-4A07-8A8C-CBBE28B209B1}" name="Table11011" displayName="Table11011" ref="A1:J41" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:J41" xr:uid="{C5E41BE5-2418-45E1-9408-F1310391CD92}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{6BF45A24-A384-44BC-9C3B-35CD0A3D42BF}" name="Var ID" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{6BF45A24-A384-44BC-9C3B-35CD0A3D42BF}" name="Var Name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{2D56EB73-45A1-4BF8-84CD-AC6E523965F9}" name="Data Type" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{D8194A20-5C02-4E07-9D01-745C3DA8465A}" name="External Access" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{C5A67F2D-FF5C-4011-9043-C208D78FF539}" name="Units" dataDxfId="6"/>
@@ -2344,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>13</v>
@@ -2355,10 +2358,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -2387,10 +2390,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
@@ -2408,7 +2411,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -2419,10 +2422,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
@@ -2451,10 +2454,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -2472,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -2483,10 +2486,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>12</v>
@@ -2515,13 +2518,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>13</v>
@@ -2536,7 +2539,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -2547,13 +2550,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>13</v>
@@ -2579,13 +2582,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>13</v>
@@ -2600,7 +2603,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -2611,13 +2614,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -2643,13 +2646,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -2664,7 +2667,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -2675,13 +2678,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -2707,13 +2710,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
@@ -2728,7 +2731,7 @@
         <v>13</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
@@ -2852,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -2895,10 +2898,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -2916,7 +2919,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -2927,10 +2930,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
@@ -2959,10 +2962,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
@@ -2980,7 +2983,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -2991,10 +2994,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -3023,10 +3026,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>12</v>
@@ -3044,7 +3047,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -3055,13 +3058,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>13</v>
@@ -3087,13 +3090,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>13</v>
@@ -3108,7 +3111,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -3119,13 +3122,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>13</v>
@@ -3151,13 +3154,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -3172,7 +3175,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -3183,13 +3186,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -3215,13 +3218,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -3236,7 +3239,7 @@
         <v>12</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -3247,13 +3250,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>13</v>
@@ -3371,13 +3374,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
@@ -3392,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -3403,13 +3406,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
@@ -3424,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>13</v>
@@ -3435,13 +3438,13 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -3456,7 +3459,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -3467,13 +3470,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>13</v>
@@ -3488,7 +3491,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -3499,13 +3502,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>13</v>
@@ -3520,7 +3523,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -3531,13 +3534,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>13</v>
@@ -3552,7 +3555,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -3563,13 +3566,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>13</v>
@@ -3584,7 +3587,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -3595,13 +3598,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>13</v>
@@ -3616,7 +3619,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -3627,13 +3630,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>13</v>
@@ -3648,7 +3651,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -3659,13 +3662,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>13</v>
@@ -3680,7 +3683,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -3691,13 +3694,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -3712,7 +3715,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -3723,13 +3726,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -3744,7 +3747,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -3755,13 +3758,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -3776,7 +3779,7 @@
         <v>12</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -3787,13 +3790,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>13</v>
@@ -3808,7 +3811,7 @@
         <v>13</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
@@ -3819,13 +3822,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>13</v>
@@ -3840,7 +3843,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -3851,13 +3854,13 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
@@ -3872,7 +3875,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -3883,13 +3886,13 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>13</v>
@@ -3904,7 +3907,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -3915,13 +3918,13 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>13</v>
@@ -3936,7 +3939,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -3947,13 +3950,13 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>13</v>
@@ -3968,7 +3971,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -3979,13 +3982,13 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>13</v>
@@ -4000,7 +4003,7 @@
         <v>19</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -4011,13 +4014,13 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>13</v>
@@ -4032,7 +4035,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -4043,13 +4046,13 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>13</v>
@@ -4064,7 +4067,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -4075,13 +4078,13 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>13</v>
@@ -4096,7 +4099,7 @@
         <v>22</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
@@ -4107,13 +4110,13 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>13</v>
@@ -4128,7 +4131,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>13</v>
@@ -4139,13 +4142,13 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>13</v>
@@ -4160,7 +4163,7 @@
         <v>24</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -4171,13 +4174,13 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>13</v>
@@ -4192,7 +4195,7 @@
         <v>25</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -4203,13 +4206,13 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>13</v>
@@ -4224,7 +4227,7 @@
         <v>26</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -4235,13 +4238,13 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>13</v>
@@ -4256,7 +4259,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -4267,13 +4270,13 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>13</v>
@@ -4288,7 +4291,7 @@
         <v>28</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -4299,13 +4302,13 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>13</v>
@@ -4320,7 +4323,7 @@
         <v>29</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -4331,13 +4334,13 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>13</v>
@@ -4352,7 +4355,7 @@
         <v>30</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -4363,13 +4366,13 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>13</v>
@@ -4384,7 +4387,7 @@
         <v>31</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -4395,13 +4398,13 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>13</v>
@@ -4416,7 +4419,7 @@
         <v>32</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -4427,13 +4430,13 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>13</v>
@@ -4448,7 +4451,7 @@
         <v>33</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -4459,13 +4462,13 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>13</v>
@@ -4480,7 +4483,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>13</v>
@@ -4491,13 +4494,13 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>13</v>
@@ -4512,7 +4515,7 @@
         <v>35</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -4523,13 +4526,13 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>13</v>
@@ -4544,7 +4547,7 @@
         <v>36</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -4555,13 +4558,13 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>13</v>
@@ -4576,7 +4579,7 @@
         <v>37</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>13</v>
@@ -4587,13 +4590,13 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>13</v>
@@ -4608,7 +4611,7 @@
         <v>38</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -4619,13 +4622,13 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>13</v>
@@ -4640,7 +4643,7 @@
         <v>39</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
